--- a/output_plant/stomata_Intermediate_steinthorsdottir_2019a.xlsx
+++ b/output_plant/stomata_Intermediate_steinthorsdottir_2019a.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <si>
     <t>eDab</t>
   </si>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">10.1016/j.palaeo.2018.01.039</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-si_steinthorsdottir_2019a.xlsx</t>
+    <t xml:space="preserve">stomata-si_steinthorsdottir_2019a_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -630,7 +630,13 @@
     <t xml:space="preserve">Mataura River</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-sr_steinthorsdottir_2019a.xlsx</t>
+    <t xml:space="preserve">Foulden Maar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiometric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stomata-sr_steinthorsdottir_2019a_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">estimates of CO2 were also made using the stomatal index proxy with the same fossil leaves</t>
@@ -2117,13 +2123,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>199</v>
@@ -2131,20 +2137,24 @@
       <c r="E7" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="F7" s="25" t="n">
+        <v>-45.516666</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>170.21666</v>
+      </c>
       <c r="H7" s="23" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="23" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K7" s="23" t="n">
-        <v>21</v>
+        <v>23.4</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>202</v>
@@ -2201,18 +2211,18 @@
       <c r="BI7" s="1"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>199</v>
@@ -2220,21 +2230,17 @@
       <c r="E8" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="25" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>167</v>
-      </c>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="23" t="n">
-        <v>22.5</v>
+        <v>19</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>23.5</v>
+        <v>21</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>201</v>
@@ -2294,33 +2300,63 @@
       <c r="BI8" s="1"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="23"/>
+      <c r="A9" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>167</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>22.5</v>
+      </c>
       <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="J9" s="23" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="26"/>
       <c r="Q9" s="26"/>
+      <c r="R9"/>
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
+      <c r="U9"/>
       <c r="V9" s="26"/>
       <c r="W9" s="26"/>
+      <c r="X9"/>
       <c r="Y9" s="24"/>
       <c r="Z9" s="24"/>
+      <c r="AA9"/>
       <c r="AB9" s="24"/>
       <c r="AC9" s="24"/>
       <c r="AD9" s="1"/>
@@ -2329,6 +2365,7 @@
       <c r="AG9" s="1"/>
       <c r="AH9" s="25"/>
       <c r="AI9" s="25"/>
+      <c r="AJ9"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
@@ -2355,32 +2392,64 @@
       <c r="BH9" s="1"/>
       <c r="BI9" s="1"/>
       <c r="BJ9" s="1"/>
-      <c r="BK9" s="1"/>
+      <c r="BK9" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="23"/>
+      <c r="A10" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>-45.516666</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>170.21666</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>23.2</v>
+      </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="J10" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="26"/>
       <c r="Q10" s="26"/>
+      <c r="R10"/>
       <c r="S10" s="24"/>
       <c r="T10" s="24"/>
+      <c r="U10"/>
       <c r="V10" s="26"/>
       <c r="W10" s="26"/>
+      <c r="X10"/>
       <c r="Y10" s="24"/>
       <c r="Z10" s="24"/>
+      <c r="AA10"/>
       <c r="AB10" s="24"/>
       <c r="AC10" s="24"/>
       <c r="AD10" s="1"/>
@@ -2389,6 +2458,7 @@
       <c r="AG10" s="1"/>
       <c r="AH10" s="25"/>
       <c r="AI10" s="25"/>
+      <c r="AJ10"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
@@ -2415,7 +2485,9 @@
       <c r="BH10" s="1"/>
       <c r="BI10" s="1"/>
       <c r="BJ10" s="1"/>
-      <c r="BK10" s="1"/>
+      <c r="BK10" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
